--- a/files/R01-R69全节点业务验收测试包/B00_基础项目资料/B00_B00-QUAL-001_TEST-B00-004_单位人员资质台账.xlsx
+++ b/files/R01-R69全节点业务验收测试包/B00_基础项目资料/B00_B00-QUAL-001_TEST-B00-004_单位人员资质台账.xlsx
@@ -2,8 +2,8 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="单位" sheetId="1" r:id="R8ed795cd521d4dbc"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="人员证书" sheetId="2" r:id="Rd6a4b0246c1a49a9"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="单位" sheetId="1" r:id="Rf46b8a805f904c47"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="人员证书" sheetId="2" r:id="R847ec2b7160949e5"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -43,7 +43,7 @@
       <x:name val="Arial Unicode MS"/>
     </x:font>
   </x:fonts>
-  <x:fills count="4">
+  <x:fills count="5">
     <x:fill>
       <x:patternFill patternType="none"/>
     </x:fill>
@@ -60,8 +60,13 @@
         <x:fgColor rgb="FFFCE8E6"/>
       </x:patternFill>
     </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFFFF3F1"/>
+      </x:patternFill>
+    </x:fill>
   </x:fills>
-  <x:borders count="9">
+  <x:borders count="17">
     <x:border/>
     <x:border>
       <x:left/>
@@ -90,12 +95,64 @@
     <x:border>
       <x:right/>
       <x:bottom/>
+    </x:border>
+    <x:border>
+      <x:left style="thin">
+        <x:color rgb="FFE6A7A2"/>
+      </x:left>
+      <x:top style="thin">
+        <x:color rgb="FFE6A7A2"/>
+      </x:top>
+    </x:border>
+    <x:border>
+      <x:top style="thin">
+        <x:color rgb="FFE6A7A2"/>
+      </x:top>
+    </x:border>
+    <x:border>
+      <x:right style="thin">
+        <x:color rgb="FFE6A7A2"/>
+      </x:right>
+      <x:top style="thin">
+        <x:color rgb="FFE6A7A2"/>
+      </x:top>
+    </x:border>
+    <x:border>
+      <x:left style="thin">
+        <x:color rgb="FFE6A7A2"/>
+      </x:left>
+    </x:border>
+    <x:border>
+      <x:right style="thin">
+        <x:color rgb="FFE6A7A2"/>
+      </x:right>
+    </x:border>
+    <x:border>
+      <x:left style="thin">
+        <x:color rgb="FFE6A7A2"/>
+      </x:left>
+      <x:bottom style="thin">
+        <x:color rgb="FFE6A7A2"/>
+      </x:bottom>
+    </x:border>
+    <x:border>
+      <x:bottom style="thin">
+        <x:color rgb="FFE6A7A2"/>
+      </x:bottom>
+    </x:border>
+    <x:border>
+      <x:right style="thin">
+        <x:color rgb="FFE6A7A2"/>
+      </x:right>
+      <x:bottom style="thin">
+        <x:color rgb="FFE6A7A2"/>
+      </x:bottom>
     </x:border>
   </x:borders>
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="41">
+  <x:cellXfs count="69">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -187,6 +244,70 @@
       <x:alignment vertical="center" wrapText="1"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="4" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="2" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="2" fillId="4" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="2" fillId="4" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="2" fillId="4" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="2" fillId="4" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="2" fillId="4" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="2" fillId="4" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="2" fillId="4" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="2" fillId="4" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="2" fillId="4" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="2" fillId="4" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="2" fillId="4" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="2" fillId="4" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="2" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="2" fillId="4" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="2" fillId="4" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="2" fillId="4" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="2" fillId="4" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="2" fillId="4" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="2" fillId="4" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="2" fillId="4" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="2" fillId="4" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="2" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="2" fillId="4" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="2" fillId="4" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="2" fillId="4" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="2" fillId="4" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment vertical="center" wrapText="1"/>
     </x:xf>
   </x:cellXfs>
@@ -238,6 +359,70 @@
     </x:dxf>
   </x:dxfs>
 </x:styleSheet>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>17</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="2190750" cy="876300"/>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="1" name="61bbd5ce-182d-44bf-a8e2-394fde4924d9"/>
+        <xdr:cNvPicPr>
+          <a:picLocks xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" r:embed="Rff2b5bd374cd4e82"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:oneCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>15</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="2190750" cy="876300"/>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="1" name="c4a58c33-c153-431f-8a47-aaedac8c217a"/>
+        <xdr:cNvPicPr>
+          <a:picLocks xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" r:embed="R8df174b1c27540f0"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:oneCellAnchor>
+</xdr:wsDr>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -437,7 +622,7 @@
   <x:cols>
     <x:col min="1" max="1" width="34" hidden="0" customWidth="1"/>
     <x:col min="2" max="2" width="24.440000534057617" hidden="0" customWidth="1"/>
-    <x:col min="3" max="3" width="12" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="16.440000534057617" hidden="0" customWidth="1"/>
     <x:col min="4" max="4" width="12" hidden="0" customWidth="1"/>
     <x:col min="5" max="5" width="12" hidden="0" customWidth="1"/>
   </x:cols>
@@ -514,33 +699,33 @@
     </x:row>
     <x:row r="7" ht="15" hidden="0" customHeight="1">
       <x:c r="A7" s="35" t="str">
-        <x:v>TEST-INSTALLATION-ORG</x:v>
+        <x:v>INSTALL-GZHG</x:v>
       </x:c>
       <x:c r="B7" s="36" t="str">
-        <x:v>TEST-压力管道安装单位</x:v>
+        <x:v>贵州化工建设有限责任公司</x:v>
       </x:c>
       <x:c r="C7" s="36" t="str">
-        <x:v>施工单位</x:v>
+        <x:v>2021年施工单位</x:v>
       </x:c>
       <x:c r="D7" s="36" t="str">
-        <x:v>合成</x:v>
+        <x:v>来源复用</x:v>
       </x:c>
       <x:c r="E7" s="37" t="str">
         <x:v>已核对</x:v>
       </x:c>
     </x:row>
-    <x:row r="8" ht="15" hidden="0" customHeight="1">
+    <x:row r="8" ht="21.600000381469727" hidden="0" customHeight="1">
       <x:c r="A8" s="35" t="str">
-        <x:v>TEST-NDT-ORG</x:v>
+        <x:v>NDT-NJJX</x:v>
       </x:c>
       <x:c r="B8" s="36" t="str">
-        <x:v>TEST-无损检测机构</x:v>
+        <x:v>南京金鑫检测工程有限责任公司</x:v>
       </x:c>
       <x:c r="C8" s="36" t="str">
-        <x:v>无损检测单位</x:v>
+        <x:v>交工资料登记无损检测单位</x:v>
       </x:c>
       <x:c r="D8" s="36" t="str">
-        <x:v>合成</x:v>
+        <x:v>来源复用</x:v>
       </x:c>
       <x:c r="E8" s="37" t="str">
         <x:v>已核对</x:v>
@@ -548,46 +733,180 @@
     </x:row>
     <x:row r="9" ht="15" hidden="0" customHeight="1">
       <x:c r="A9" s="35" t="str">
-        <x:v>TEST-LAB-ORG</x:v>
+        <x:v>NDT-GZSH</x:v>
       </x:c>
       <x:c r="B9" s="36" t="str">
-        <x:v>TEST-材料与理化试验机构</x:v>
+        <x:v>广州声华科技股份有限公司</x:v>
       </x:c>
       <x:c r="C9" s="36" t="str">
-        <x:v>试验单位</x:v>
+        <x:v>2021年RT报告签发单位</x:v>
       </x:c>
       <x:c r="D9" s="36" t="str">
-        <x:v>合成</x:v>
+        <x:v>来源复用</x:v>
       </x:c>
       <x:c r="E9" s="37" t="str">
         <x:v>已核对</x:v>
       </x:c>
     </x:row>
     <x:row r="10" ht="15" hidden="0" customHeight="1">
-      <x:c r="A10" s="38" t="str">
+      <x:c r="A10" s="35" t="str">
+        <x:v>SUPV-GD-ZH</x:v>
+      </x:c>
+      <x:c r="B10" s="36" t="str">
+        <x:v>广东省特种设备检测研究院珠海检测院</x:v>
+      </x:c>
+      <x:c r="C10" s="36" t="str">
+        <x:v>2021年安装监督检验单位</x:v>
+      </x:c>
+      <x:c r="D10" s="36" t="str">
+        <x:v>来源复用</x:v>
+      </x:c>
+      <x:c r="E10" s="37" t="str">
+        <x:v>已核对</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="11" ht="15" hidden="0" customHeight="1">
+      <x:c r="A11" s="35" t="str">
+        <x:v>MFR-GH</x:v>
+      </x:c>
+      <x:c r="B11" s="36" t="str">
+        <x:v>河北广浩管件有限公司</x:v>
+      </x:c>
+      <x:c r="C11" s="36" t="str">
+        <x:v>来源管件制造单位</x:v>
+      </x:c>
+      <x:c r="D11" s="36" t="str">
+        <x:v>来源复用</x:v>
+      </x:c>
+      <x:c r="E11" s="37" t="str">
+        <x:v>已核对</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="12" ht="15" hidden="0" customHeight="1">
+      <x:c r="A12" s="35" t="str">
+        <x:v>MFR-LB</x:v>
+      </x:c>
+      <x:c r="B12" s="36" t="str">
+        <x:v>烟台鲁宝钢管有限责任公司</x:v>
+      </x:c>
+      <x:c r="C12" s="36" t="str">
+        <x:v>来源钢管制造单位</x:v>
+      </x:c>
+      <x:c r="D12" s="36" t="str">
+        <x:v>来源复用</x:v>
+      </x:c>
+      <x:c r="E12" s="37" t="str">
+        <x:v>已核对</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="13" ht="15" hidden="0" customHeight="1">
+      <x:c r="A13" s="35" t="str">
+        <x:v>TEST-INSTALLATION-ORG</x:v>
+      </x:c>
+      <x:c r="B13" s="36" t="str">
+        <x:v>TEST-压力管道安装单位</x:v>
+      </x:c>
+      <x:c r="C13" s="36" t="str">
+        <x:v>施工单位</x:v>
+      </x:c>
+      <x:c r="D13" s="36" t="str">
+        <x:v>合成</x:v>
+      </x:c>
+      <x:c r="E13" s="37" t="str">
+        <x:v>已核对</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="14" ht="15" hidden="0" customHeight="1">
+      <x:c r="A14" s="35" t="str">
+        <x:v>TEST-NDT-ORG</x:v>
+      </x:c>
+      <x:c r="B14" s="36" t="str">
+        <x:v>TEST-无损检测机构</x:v>
+      </x:c>
+      <x:c r="C14" s="36" t="str">
+        <x:v>无损检测单位</x:v>
+      </x:c>
+      <x:c r="D14" s="36" t="str">
+        <x:v>合成</x:v>
+      </x:c>
+      <x:c r="E14" s="37" t="str">
+        <x:v>已核对</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="15" ht="15" hidden="0" customHeight="1">
+      <x:c r="A15" s="35" t="str">
+        <x:v>TEST-LAB-ORG</x:v>
+      </x:c>
+      <x:c r="B15" s="36" t="str">
+        <x:v>TEST-材料与理化试验机构</x:v>
+      </x:c>
+      <x:c r="C15" s="36" t="str">
+        <x:v>试验单位</x:v>
+      </x:c>
+      <x:c r="D15" s="36" t="str">
+        <x:v>合成</x:v>
+      </x:c>
+      <x:c r="E15" s="37" t="str">
+        <x:v>已核对</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="16" ht="15" hidden="0" customHeight="1">
+      <x:c r="A16" s="38" t="str">
         <x:v>TEST-SUPERVISION-ORG</x:v>
       </x:c>
-      <x:c r="B10" s="39" t="str">
+      <x:c r="B16" s="39" t="str">
         <x:v>TEST-监督检验角色单位</x:v>
       </x:c>
-      <x:c r="C10" s="39" t="str">
+      <x:c r="C16" s="39" t="str">
         <x:v>监检角色</x:v>
       </x:c>
-      <x:c r="D10" s="39" t="str">
+      <x:c r="D16" s="39" t="str">
         <x:v>合成</x:v>
       </x:c>
-      <x:c r="E10" s="40" t="str">
+      <x:c r="E16" s="40" t="str">
         <x:v>已核对</x:v>
       </x:c>
     </x:row>
-    <x:row r="11"/>
-    <x:row r="12"/>
+    <x:row r="17"/>
+    <x:row r="18" ht="15" hidden="0" customHeight="1">
+      <x:c r="A18" s="60" t="str">
+        <x:v>电子签署（测试）｜工程质量测试专用章</x:v>
+      </x:c>
+      <x:c r="B18" s="61"/>
+      <x:c r="C18" s="61"/>
+      <x:c r="D18" s="61"/>
+      <x:c r="E18" s="62"/>
+    </x:row>
+    <x:row r="19" ht="15" hidden="0" customHeight="1">
+      <x:c r="A19" s="63"/>
+      <x:c r="B19" s="64"/>
+      <x:c r="C19" s="64"/>
+      <x:c r="D19" s="64"/>
+      <x:c r="E19" s="65"/>
+    </x:row>
+    <x:row r="20" ht="15" hidden="0" customHeight="1">
+      <x:c r="A20" s="63"/>
+      <x:c r="B20" s="64"/>
+      <x:c r="C20" s="64"/>
+      <x:c r="D20" s="64"/>
+      <x:c r="E20" s="65"/>
+    </x:row>
+    <x:row r="21" ht="15" hidden="0" customHeight="1">
+      <x:c r="A21" s="66"/>
+      <x:c r="B21" s="67"/>
+      <x:c r="C21" s="67"/>
+      <x:c r="D21" s="67"/>
+      <x:c r="E21" s="68"/>
+    </x:row>
+    <x:row r="22"/>
+    <x:row r="23"/>
   </x:sheetData>
   <x:mergeCells>
     <x:mergeCell ref="A1:E1"/>
     <x:mergeCell ref="A2:E2"/>
+    <x:mergeCell ref="A18:C18"/>
   </x:mergeCells>
-  <x:conditionalFormatting sqref="A5:E10">
+  <x:conditionalFormatting sqref="A5:E16">
     <x:cfRule type="expression" dxfId="0" priority="1">
       <x:formula>OR(ISNUMBER(SEARCH("不合格",A5)),ISNUMBER(SEARCH("异常",A5)))</x:formula>
     </x:cfRule>
@@ -596,6 +915,7 @@
     </x:cfRule>
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R944627912d5948c6"/>
 </x:worksheet>
 </file>
 
@@ -605,7 +925,7 @@
   <x:cols>
     <x:col min="1" max="1" width="34" hidden="0" customWidth="1"/>
     <x:col min="2" max="2" width="12.4399995803833" hidden="0" customWidth="1"/>
-    <x:col min="3" max="3" width="12" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="13.779999732971191" hidden="0" customWidth="1"/>
     <x:col min="4" max="4" width="17" hidden="0" customWidth="1"/>
     <x:col min="5" max="5" width="12" hidden="0" customWidth="1"/>
     <x:col min="6" max="6" width="12" hidden="0" customWidth="1"/>
@@ -621,7 +941,7 @@
       <x:c r="E1" s="4"/>
       <x:c r="F1" s="4"/>
     </x:row>
-    <x:row r="2" ht="21.600000381469727" hidden="0" customHeight="1">
+    <x:row r="2" ht="15" hidden="0" customHeight="1">
       <x:c r="A2" s="9" t="str">
         <x:v>测试专用／合成资料／不得用于真实工程｜TEST-ONLY / SYNTHETIC / NOT FOR REAL ENGINEERING USE｜文件编号：TEST-B00-004｜版本：0｜日期：2026-05-20</x:v>
       </x:c>
@@ -654,13 +974,13 @@
     </x:row>
     <x:row r="5" ht="15" hidden="0" customHeight="1">
       <x:c r="A5" s="32" t="str">
-        <x:v>TEST-PER-DES-01</x:v>
+        <x:v>PER-YDH</x:v>
       </x:c>
       <x:c r="B5" s="33" t="str">
-        <x:v>测试设计负责人甲</x:v>
+        <x:v>杨道红</x:v>
       </x:c>
       <x:c r="C5" s="33" t="str">
-        <x:v>设计</x:v>
+        <x:v>来源设计许可印章人员</x:v>
       </x:c>
       <x:c r="D5" s="33" t="str">
         <x:v>TEST-ROLE-RECORD</x:v>
@@ -674,13 +994,13 @@
     </x:row>
     <x:row r="6" ht="15" hidden="0" customHeight="1">
       <x:c r="A6" s="35" t="str">
-        <x:v>TEST-PER-CHK-01</x:v>
+        <x:v>PER-ZWH</x:v>
       </x:c>
       <x:c r="B6" s="36" t="str">
-        <x:v>测试校核负责人乙</x:v>
+        <x:v>赵伟辉</x:v>
       </x:c>
       <x:c r="C6" s="36" t="str">
-        <x:v>校核</x:v>
+        <x:v>2021年交工记录焊工</x:v>
       </x:c>
       <x:c r="D6" s="36" t="str">
         <x:v>TEST-ROLE-RECORD</x:v>
@@ -694,13 +1014,13 @@
     </x:row>
     <x:row r="7" ht="15" hidden="0" customHeight="1">
       <x:c r="A7" s="35" t="str">
-        <x:v>TEST-PER-APR-01</x:v>
+        <x:v>PER-PBX</x:v>
       </x:c>
       <x:c r="B7" s="36" t="str">
-        <x:v>测试批准负责人丙</x:v>
+        <x:v>庞柏鑫</x:v>
       </x:c>
       <x:c r="C7" s="36" t="str">
-        <x:v>批准</x:v>
+        <x:v>2021年交工记录焊工</x:v>
       </x:c>
       <x:c r="D7" s="36" t="str">
         <x:v>TEST-ROLE-RECORD</x:v>
@@ -712,18 +1032,18 @@
         <x:v>有效（测试）</x:v>
       </x:c>
     </x:row>
-    <x:row r="8" ht="21.600000381469727" hidden="0" customHeight="1">
+    <x:row r="8" ht="15" hidden="0" customHeight="1">
       <x:c r="A8" s="35" t="str">
-        <x:v>TEST-PER-QA-01</x:v>
+        <x:v>PER-ZJX</x:v>
       </x:c>
       <x:c r="B8" s="36" t="str">
-        <x:v>测试质量责任人员丁</x:v>
+        <x:v>赵俊祥</x:v>
       </x:c>
       <x:c r="C8" s="36" t="str">
-        <x:v>质量保证</x:v>
+        <x:v>来源焊工资格证人员</x:v>
       </x:c>
       <x:c r="D8" s="36" t="str">
-        <x:v>TEST-ROLE-RECORD</x:v>
+        <x:v>TS2100000099937</x:v>
       </x:c>
       <x:c r="E8" s="36" t="str">
         <x:v>测试资质数据页</x:v>
@@ -734,16 +1054,16 @@
     </x:row>
     <x:row r="9" ht="15" hidden="0" customHeight="1">
       <x:c r="A9" s="35" t="str">
-        <x:v>TEST-PER-WELD-01</x:v>
+        <x:v>TEST-PER-DES-01</x:v>
       </x:c>
       <x:c r="B9" s="36" t="str">
-        <x:v>测试焊工甲</x:v>
+        <x:v>测试设计负责人甲</x:v>
       </x:c>
       <x:c r="C9" s="36" t="str">
-        <x:v>焊工</x:v>
+        <x:v>设计</x:v>
       </x:c>
       <x:c r="D9" s="36" t="str">
-        <x:v>TEST-CERT-WELDER-001</x:v>
+        <x:v>TEST-ROLE-RECORD</x:v>
       </x:c>
       <x:c r="E9" s="36" t="str">
         <x:v>测试资质数据页</x:v>
@@ -753,33 +1073,149 @@
       </x:c>
     </x:row>
     <x:row r="10" ht="15" hidden="0" customHeight="1">
-      <x:c r="A10" s="38" t="str">
+      <x:c r="A10" s="35" t="str">
+        <x:v>TEST-PER-CHK-01</x:v>
+      </x:c>
+      <x:c r="B10" s="36" t="str">
+        <x:v>测试校核负责人乙</x:v>
+      </x:c>
+      <x:c r="C10" s="36" t="str">
+        <x:v>校核</x:v>
+      </x:c>
+      <x:c r="D10" s="36" t="str">
+        <x:v>TEST-ROLE-RECORD</x:v>
+      </x:c>
+      <x:c r="E10" s="36" t="str">
+        <x:v>测试资质数据页</x:v>
+      </x:c>
+      <x:c r="F10" s="37" t="str">
+        <x:v>有效（测试）</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="11" ht="15" hidden="0" customHeight="1">
+      <x:c r="A11" s="35" t="str">
+        <x:v>TEST-PER-APR-01</x:v>
+      </x:c>
+      <x:c r="B11" s="36" t="str">
+        <x:v>测试批准负责人丙</x:v>
+      </x:c>
+      <x:c r="C11" s="36" t="str">
+        <x:v>批准</x:v>
+      </x:c>
+      <x:c r="D11" s="36" t="str">
+        <x:v>TEST-ROLE-RECORD</x:v>
+      </x:c>
+      <x:c r="E11" s="36" t="str">
+        <x:v>测试资质数据页</x:v>
+      </x:c>
+      <x:c r="F11" s="37" t="str">
+        <x:v>有效（测试）</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="12" ht="21.600000381469727" hidden="0" customHeight="1">
+      <x:c r="A12" s="35" t="str">
+        <x:v>TEST-PER-QA-01</x:v>
+      </x:c>
+      <x:c r="B12" s="36" t="str">
+        <x:v>测试质量责任人员丁</x:v>
+      </x:c>
+      <x:c r="C12" s="36" t="str">
+        <x:v>质量保证</x:v>
+      </x:c>
+      <x:c r="D12" s="36" t="str">
+        <x:v>TEST-ROLE-RECORD</x:v>
+      </x:c>
+      <x:c r="E12" s="36" t="str">
+        <x:v>测试资质数据页</x:v>
+      </x:c>
+      <x:c r="F12" s="37" t="str">
+        <x:v>有效（测试）</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="13" ht="15" hidden="0" customHeight="1">
+      <x:c r="A13" s="35" t="str">
+        <x:v>TEST-PER-WELD-01</x:v>
+      </x:c>
+      <x:c r="B13" s="36" t="str">
+        <x:v>测试焊工甲</x:v>
+      </x:c>
+      <x:c r="C13" s="36" t="str">
+        <x:v>焊工</x:v>
+      </x:c>
+      <x:c r="D13" s="36" t="str">
+        <x:v>TEST-CERT-WELDER-001</x:v>
+      </x:c>
+      <x:c r="E13" s="36" t="str">
+        <x:v>测试资质数据页</x:v>
+      </x:c>
+      <x:c r="F13" s="37" t="str">
+        <x:v>有效（测试）</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="14" ht="15" hidden="0" customHeight="1">
+      <x:c r="A14" s="38" t="str">
         <x:v>TEST-PER-NDT-01</x:v>
       </x:c>
-      <x:c r="B10" s="39" t="str">
+      <x:c r="B14" s="39" t="str">
         <x:v>测试检测人员乙</x:v>
       </x:c>
-      <x:c r="C10" s="39" t="str">
+      <x:c r="C14" s="39" t="str">
         <x:v>无损检测</x:v>
       </x:c>
-      <x:c r="D10" s="39" t="str">
+      <x:c r="D14" s="39" t="str">
         <x:v>TEST-CERT-NDT-PER-001</x:v>
       </x:c>
-      <x:c r="E10" s="39" t="str">
+      <x:c r="E14" s="39" t="str">
         <x:v>测试资质数据页</x:v>
       </x:c>
-      <x:c r="F10" s="40" t="str">
+      <x:c r="F14" s="40" t="str">
         <x:v>有效（测试）</x:v>
       </x:c>
     </x:row>
-    <x:row r="11"/>
-    <x:row r="12"/>
+    <x:row r="15"/>
+    <x:row r="16" ht="15" hidden="0" customHeight="1">
+      <x:c r="A16" s="60" t="str">
+        <x:v>电子签署（测试）｜工程质量测试专用章</x:v>
+      </x:c>
+      <x:c r="B16" s="61"/>
+      <x:c r="C16" s="61"/>
+      <x:c r="D16" s="61"/>
+      <x:c r="E16" s="61"/>
+      <x:c r="F16" s="62"/>
+    </x:row>
+    <x:row r="17" ht="15" hidden="0" customHeight="1">
+      <x:c r="A17" s="63"/>
+      <x:c r="B17" s="64"/>
+      <x:c r="C17" s="64"/>
+      <x:c r="D17" s="64"/>
+      <x:c r="E17" s="64"/>
+      <x:c r="F17" s="65"/>
+    </x:row>
+    <x:row r="18" ht="15" hidden="0" customHeight="1">
+      <x:c r="A18" s="63"/>
+      <x:c r="B18" s="64"/>
+      <x:c r="C18" s="64"/>
+      <x:c r="D18" s="64"/>
+      <x:c r="E18" s="64"/>
+      <x:c r="F18" s="65"/>
+    </x:row>
+    <x:row r="19" ht="15" hidden="0" customHeight="1">
+      <x:c r="A19" s="66"/>
+      <x:c r="B19" s="67"/>
+      <x:c r="C19" s="67"/>
+      <x:c r="D19" s="67"/>
+      <x:c r="E19" s="67"/>
+      <x:c r="F19" s="68"/>
+    </x:row>
+    <x:row r="20"/>
+    <x:row r="21"/>
   </x:sheetData>
   <x:mergeCells>
     <x:mergeCell ref="A1:F1"/>
     <x:mergeCell ref="A2:F2"/>
+    <x:mergeCell ref="A16:C16"/>
   </x:mergeCells>
-  <x:conditionalFormatting sqref="A5:F10">
+  <x:conditionalFormatting sqref="A5:F14">
     <x:cfRule type="expression" dxfId="2" priority="1">
       <x:formula>OR(ISNUMBER(SEARCH("不合格",A5)),ISNUMBER(SEARCH("异常",A5)))</x:formula>
     </x:cfRule>
@@ -788,5 +1224,6 @@
     </x:cfRule>
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R6a21ca34d09246d6"/>
 </x:worksheet>
 </file>